--- a/WorkBot/refactor-experimental/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20251116.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20251116.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,195 @@
         <v>545.1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>126160</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peanut Butter - Bulk</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60.21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>123170</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Glaze - Maple</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>124440</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8 Grain</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>205.56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>140600</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Flour - Rice</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>108900</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seeds - Poppy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>110.68</v>
+      </c>
+      <c r="E7" t="n">
+        <v>110.68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>123060</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Glaze - Donut</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>108970</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Garlic - Dry Minced</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>157.43</v>
+      </c>
+      <c r="E9" t="n">
+        <v>472.29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4100760</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Apple Cinnamon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4100860</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Cinnamon Walnut</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="E11" t="n">
+        <v>57.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
